--- a/data_raw/city_expenditure.xlsx
+++ b/data_raw/city_expenditure.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>地方一般公共预算支出(亿元)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2302 +420,2458 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>地方一般公共预算支出(亿元)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1795.566</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>2181.678</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>2593.9161</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>2989.65</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>3302.8862</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>3914.88</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>4184.017</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>4528.6079</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>4923.4372</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>6191.5601</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>6918.94</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>7547.6208</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>8351.5376</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>8179.284</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>8102.112</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>8430.8562</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>9393</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>9638.51</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>9874.838100000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>49.5342</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>68.31529999999999</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>99.34999999999999</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>133.8811</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>159.6108</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>238.4851</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>295.6004</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>353.2024</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>404.8053</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>446.6619</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>417.5628</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>458.5812</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>659.7858</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>620.2786</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>536.8738</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>419.5874</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>455.7678</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>504.0517</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>465.5229</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>63.1321</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>83.29819999999999</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>99.6601</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>119.8342</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>146.9264</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>175.4806</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>202.5976</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>242.3426</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>280.1041</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>344.0019</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>424.1597</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>429.3614</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>465.6417</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>456.6617</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>486.2409</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>484.589</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>498.7969</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>502.9172</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>547.6361000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1296.8389</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1649.5023</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1959.2857</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2319.3658</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>2717.3174</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3245.23</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>3685.3076</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>4173.6563</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>4524.669</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>5737.7011</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>6406.77</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>6824.5284</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>7471.4332</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>7408.1876</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>7116.1764</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>7205.1201</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>7469.1547</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>7971.25</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>8396.486000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>262.4614</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>342.9386</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>404.6656</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>461.2662</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>542.1812</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>666.2056</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>769.6569</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>850.9085</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>921.2047</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1045.57</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>1173.84</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>1354.0873</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>1532.7156</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>1658.07</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>1754.619</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>1817.728</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>1828.6941</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>1838.6959</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>1705.2595</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>93.07810000000001</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>118.0007</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>166.083</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>203.5519</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>261.2785</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>302.3075</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>376.5096</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>418.3976</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>465.7759</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>526.7231</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>586.9793</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>646.3707000000001</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>697.9853000000001</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>789.1986000000001</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>819.8554</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>778</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>838.9332000000001</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>816.4829</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>796.9934</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>93.3749</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>116.8596</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>148.17</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>181.7495</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>232.0305</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>299.3677</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>345.5062</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>419.3652</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>473.1561</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>543.1789</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>583.2565</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>653.1223</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>752.4136999999999</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>834.1066</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>838.1744</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>870.0084000000001</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>939.0409</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>925.5526</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>940.0703</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>159.1253</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>198.6559</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>238.0896</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>268.0527</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>306.9468</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>389.0726</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>460.9779</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>516.7402</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>548.2525000000001</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>651.1704999999999</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>758.6381</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>797.0976000000001</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>892.4985</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>912.977</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>976.9054</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>1060.0015</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>1088.7431</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>1084.6541</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>1059.1976</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>102.8869</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>167.0789</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>222.2517</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>245.8575</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>317.7157</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>474.8895</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>572.0987</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>630.8885</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>698.7901000000001</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>772.6647</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>859.8502999999999</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>965.3444</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>1004.9099</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>1122.6669</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>1164.3459</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>1223.7236</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>1380.1794</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>1411.3371</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>1581.0585</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>75.49850000000001</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>100.5133</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>133.1795</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>165.1584</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>177.28</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>255.668</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>275.3195</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>294.8353</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>310.9084</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>360.645</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>419.9738</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>403.0357</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>356.7396</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>417.9245</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>438.5688</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>420.7504</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>420.9756</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>592.973</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>581.6105</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>194.6839</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>232.3833</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>301.2746</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>348.4127</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>452.9706</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>557.1368</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>643.5756</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>709.7811</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>740.078</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>824.8444</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>876.2945</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>958.4675999999999</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>962.1654</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>1101.1389</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>1162.2493</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>992.0759</v>
       </c>
-      <c r="S12">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>1080.697</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>1257.5552</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>266.5249</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>344.5728</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>410.0013</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>471.1648</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>611.4743</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>734.9406</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>890.9589999999999</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>1083.536</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>989.4552</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>910.6922</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>870.2782999999999</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>919.8403</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>1001.4898</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>1016.2849</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>1001.9838</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>980.0549</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>991.0839</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>1013.5047</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>1085.1441</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>543.1219</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>674.3262</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>867.7245</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1124.2778</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1376.8395</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1796.33</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>2143.2125</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>2549.2061</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>2884.6993</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>3232.3507</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>3699.43</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>3282.5404</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>3103.1579</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>3555.7052</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>3151.3505</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>3152.5478</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>2729.8298</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>3280.42</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>3627.181</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>95.4238</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>155.8029</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>152.8553</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>159.9051</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>189.6358</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>239.3147</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>277.4437</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>319.109</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>322.6934</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>419.9913</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>424.0666</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>479.0558</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>542.4589</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>610.553</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>647.3448</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>628.9857</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>715.8959</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>777.2628999999999</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>744.3766000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>292.6969</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>371.04</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>439.4083</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>506.0788</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>600.7447</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>750.7233</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>828.4437</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>939.8939</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>1000.8563</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>1252.6362</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>1289.2601</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>1410.6049</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>1594.1</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>1767.8895</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>1742.0878</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>1944.4158</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>2187.8133</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>2235.0944</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>2230.3651</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>506.7899</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>623.6917</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>713.3508</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>789.9155</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>977.3199</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>1181.25</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1343.6451</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1386.1349</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1436.2226</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>1727.7176</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>1943.7465</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>2186.013</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>2506.1818</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>2865.3263</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>2952.6468</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>3021.1834</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>3022.4506</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>2971.6481</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>2782.4982</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>252.2439</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>356.0453</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>506.4309</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>600.9694</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>777.38</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>857.8696</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>983.8477</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>1161.7542</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>1340.0037</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>1468.4242</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>1595.8949</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>1756.6621</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>1837.4238</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>2006.9493</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>2159.4765</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>2237.6872</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>2435.0108</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>2586.8282</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>2610.3949</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>15.6896</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>24.6227</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>33.0167</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>37.7316</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>51.3496</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>75.6271</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="n">
         <v>106.9009</v>
       </c>
-      <c r="I19">
+      <c r="I19" t="n">
         <v>131.9166</v>
       </c>
-      <c r="J19">
+      <c r="J19" t="n">
         <v>169.4872</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="n">
         <v>200.3958</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>248.105</v>
       </c>
-      <c r="M19">
+      <c r="M19" t="n">
         <v>257.4658</v>
       </c>
-      <c r="N19">
+      <c r="N19" t="n">
         <v>300.1179</v>
       </c>
-      <c r="O19">
+      <c r="O19" t="n">
         <v>365.4116</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="n">
         <v>349.6638</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" t="n">
         <v>318.3815</v>
       </c>
-      <c r="R19">
+      <c r="R19" t="n">
         <v>355.3345</v>
       </c>
-      <c r="S19">
+      <c r="S19" t="n">
         <v>452.1217</v>
       </c>
-      <c r="T19">
+      <c r="T19" t="n">
         <v>465.3495</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>133.6765</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>164.654</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>233.4865</v>
       </c>
-      <c r="F20">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
         <v>346.308</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>441.7322</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>525.5359999999999</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>585.761</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>593.6558</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>615.4909</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>688.4046</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>775.9012</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>756.8044</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>820.859</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>875.0545</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>928.1565000000001</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>863.3161</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>837.7916</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>842.8486</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>275.4809</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>335.7153</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>419.6674</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>490.3983</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>616.5836</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>747.5108</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>786.28</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>855.737</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>961.1771</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>1205.4777</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>1404.3065</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>1540.9156</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>1717.0834</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>1952.853</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>2069.6554</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>2392.0396</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>2542.0894</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>2636.227</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>2690.354</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>257.8102</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>307.2345</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>377.8847</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>503.643</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>583.5453</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>765.0426</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>885.5477</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>1122.8838</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>1175.1039</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>1338.0508</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>1524.6791</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>1728.2839</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>1929.3075</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>2237.1003</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>2407.8114</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>2215.9673</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>2223.1481</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>2204.0782</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>2480.996</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>268.7649</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>339.6754</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>406.7372</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>475.8822</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>516.6242</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>639.2904</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>766.0854</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>881.2817</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>914.3712</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>808.5751</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>825.3935</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>855.0151</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>965.4417</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>1047.646</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>1074.0503</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>1032.5049</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>1053.5872</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>1084.0553</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>1160.6947</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>146.9762</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>179.9787</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>221.319</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>259.9178</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>336.8037</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>396.8831</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>465.6731</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>519.319</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>571.4138</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>658.1813</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>741.2641</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>834.0599999999999</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>1018.2539</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>1197.3158</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>1288.7953</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>1293.0814</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>1225.5733</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>1365.2948</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>1397.1495</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>32.2454</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>43.2058</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>46.7882</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>66.6116</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>78.9877</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>99.4265</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>113.845</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>131.9978</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>150.92</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>170.9331</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>200.3</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>198.3183</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>238.2473</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>265.8645</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>307.0836</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>274.258</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>332.6785</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>369.5399</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>372.0654</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>571.4231</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>727.9563000000001</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>889.8555</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>1000.8394</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1265.2699</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>1590.5599</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>1565.7078</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>1690.828</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>2166.14</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>3521.6708</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>4211.0429</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>4593.8003</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>4282.5379</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>4552.7336</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>4177.7162</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>4570.2233</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>4997.3834</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>5012.067</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>4700.8708</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>128.2462</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>163.1692</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>193.7869</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>240.9171</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>305.1647</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>403.5381</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>464.0932</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>522.9442</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>566.4878</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>682.3857</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>746.1188</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>806.7284</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>991.6127</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>1051.3884</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>1142.2265</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>1152.7442</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>1250.4267</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>1274.8334</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>1274.6883</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>110.0589</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>143.0922</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>178.1952</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>205.0925</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>262.4208</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>363.3008</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>410.7344</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>533.8424</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>574.8081</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>725.9345</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>829.9274</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>938.8572</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>924.7551999999999</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>949.7604</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>951.4035</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>925.2559</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>1006.0892</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>1004.904</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>1025.4841</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>34.3058</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>45.0463</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>67.2512</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>85.1191</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>108.9186</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>150.0435</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>185.323</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>207.5698</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>248.1367</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>280.0252</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>287.805</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>288.3747</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>297.4766</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>328.0436</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>329.5111</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>343.8044</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>339.0356</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>418.7512</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>400.9837</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>119.2193</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>161.2536</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>226.9897</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>276.8502</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>371.6175</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>494.575</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>597.4937</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>729.8119</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>819.5366</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>917.24</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>942.5238000000001</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>1045.0925</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>1151.8741</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>1247.0153</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>1347.5804</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>1474.6219</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>1569.8087</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>1730.4672</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>1561.8498</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>88.2349</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>106.4287</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>142.2818</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>169.8423</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>204.3801</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>277.3807</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>349.3275</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>393.602</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>448.6298</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>503.5189</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>525.2621</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>582.4776000000001</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>624.2193</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>718.8224</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>678.1587</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>633.4063</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>727.4549</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>778.6135</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>693.0531999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>187.6587</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>240.6758</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>289.5018</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>353.0483</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>426.7968</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>566.5806</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>700.698</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>816.1571</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>918.5111000000001</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>1106.0158</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>1321.5255</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>1514.9533</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>1763.3376</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>1910.6727</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>1720.18</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>1624.4403</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>1456.408</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>1519.6232</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>1525.7095</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>594.2542999999999</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>768.3886</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>1016.0112</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>1292.0928</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>1709.0353</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>2570.24</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>3046.3599</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>3062.2848</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>3304.3884</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>3791.9973</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>4001.81</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>4336.28</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>4540.9487</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>4847.6795</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>4893.9461</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>4835.0551</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>4892.7688</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>5304.56</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>5621.2108</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>36.1239</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>48.4708</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>63.043</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>72.49890000000001</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>119.9157</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>147.2515</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>186.7446</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>220.5311</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>263.9036</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>309.2658</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>331.0717</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>341.8283</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>363.2756</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>346.4668</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>332.3605</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>291.6915</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>356.5547</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>438.1513</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>444.4561</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>146.6748</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>181.5633</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>240.3306</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>306.0062</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>382.9323</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>518.6814000000001</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>555.5117</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>632.9668</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>675.8377</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>765.7246</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>770.5743</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>875.7334</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>894.3429</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>896.022</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>1084.1364</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>966.4851</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>976.6704</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>1074.9675</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>1056.2112</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>167.1873</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>218.1733</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>260.5584</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>314.082</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>403.3349</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>520.8876</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>624.6207000000001</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>701.8238</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>802.3838</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>924.9992</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>1041.4331</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>1182.6043</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>1300.7895</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>1425.981</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>1501.2319</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>1541.5932</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>1566.2586</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>1626.8337</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>1663.9383</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>236.7875</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>321.1777</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>369.4111</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>433.5754</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>532.3887999999999</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>658.0605</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>765.9801</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>1014.2273</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>1074.7138</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>1222.8664</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>1352.8516</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>1403.0252</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>1559.7764</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>1575.9729</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>1584.6485</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>1706.7635</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>1696.1652</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>1718.7995</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>1720.4231</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_raw/city_expenditure.xlsx
+++ b/data_raw/city_expenditure.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,11 +529,6 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -598,7 +593,6 @@
       <c r="T2" t="n">
         <v>9874.838100000001</v>
       </c>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -663,7 +657,6 @@
       <c r="T3" t="n">
         <v>465.5229</v>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -728,7 +721,6 @@
       <c r="T4" t="n">
         <v>547.6361000000001</v>
       </c>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -793,7 +785,6 @@
       <c r="T5" t="n">
         <v>8396.486000000001</v>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -858,7 +849,6 @@
       <c r="T6" t="n">
         <v>1705.2595</v>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -923,7 +913,6 @@
       <c r="T7" t="n">
         <v>796.9934</v>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -988,7 +977,6 @@
       <c r="T8" t="n">
         <v>940.0703</v>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1053,7 +1041,6 @@
       <c r="T9" t="n">
         <v>1059.1976</v>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1118,7 +1105,6 @@
       <c r="T10" t="n">
         <v>1581.0585</v>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1183,7 +1169,6 @@
       <c r="T11" t="n">
         <v>581.6105</v>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1246,7 +1231,6 @@
       <c r="T12" t="n">
         <v>1257.5552</v>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1311,7 +1295,6 @@
       <c r="T13" t="n">
         <v>1085.1441</v>
       </c>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1376,7 +1359,6 @@
       <c r="T14" t="n">
         <v>3627.181</v>
       </c>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1441,7 +1423,6 @@
       <c r="T15" t="n">
         <v>744.3766000000001</v>
       </c>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1506,7 +1487,6 @@
       <c r="T16" t="n">
         <v>2230.3651</v>
       </c>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1571,7 +1551,6 @@
       <c r="T17" t="n">
         <v>2782.4982</v>
       </c>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1636,7 +1615,6 @@
       <c r="T18" t="n">
         <v>2610.3949</v>
       </c>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1701,7 +1679,6 @@
       <c r="T19" t="n">
         <v>465.3495</v>
       </c>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1764,7 +1741,6 @@
       <c r="T20" t="n">
         <v>842.8486</v>
       </c>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1829,7 +1805,6 @@
       <c r="T21" t="n">
         <v>2690.354</v>
       </c>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1894,7 +1869,6 @@
       <c r="T22" t="n">
         <v>2480.996</v>
       </c>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1959,7 +1933,6 @@
       <c r="T23" t="n">
         <v>1160.6947</v>
       </c>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2024,7 +1997,6 @@
       <c r="T24" t="n">
         <v>1397.1495</v>
       </c>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2089,7 +2061,6 @@
       <c r="T25" t="n">
         <v>372.0654</v>
       </c>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2154,7 +2125,6 @@
       <c r="T26" t="n">
         <v>4700.8708</v>
       </c>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2219,7 +2189,6 @@
       <c r="T27" t="n">
         <v>1274.6883</v>
       </c>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2284,7 +2253,6 @@
       <c r="T28" t="n">
         <v>1025.4841</v>
       </c>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2349,7 +2317,6 @@
       <c r="T29" t="n">
         <v>400.9837</v>
       </c>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2414,7 +2381,6 @@
       <c r="T30" t="n">
         <v>1561.8498</v>
       </c>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2479,7 +2445,6 @@
       <c r="T31" t="n">
         <v>693.0531999999999</v>
       </c>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2544,7 +2509,6 @@
       <c r="T32" t="n">
         <v>1525.7095</v>
       </c>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2609,7 +2573,6 @@
       <c r="T33" t="n">
         <v>5621.2108</v>
       </c>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2674,7 +2637,6 @@
       <c r="T34" t="n">
         <v>444.4561</v>
       </c>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -2739,7 +2701,6 @@
       <c r="T35" t="n">
         <v>1056.2112</v>
       </c>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -2804,7 +2765,6 @@
       <c r="T36" t="n">
         <v>1663.9383</v>
       </c>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2869,7 +2829,6 @@
       <c r="T37" t="n">
         <v>1720.4231</v>
       </c>
-      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
